--- a/services/platform-api/src/main/resources/templates/评分记录汇总表模板.xlsx
+++ b/services/platform-api/src/main/resources/templates/评分记录汇总表模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="评分记录汇总表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <t>评分记录汇总表</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>试题6</t>
+  </si>
+  <si>
+    <t>试题7</t>
+  </si>
+  <si>
+    <t>试题8</t>
   </si>
   <si>
     <t>合计
@@ -116,7 +122,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -129,6 +135,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -483,7 +496,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -495,6 +508,96 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -609,168 +712,179 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1306,524 +1420,644 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="3.625" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="7" width="3.125" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
-    <col min="9" max="13" width="3.125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="19" width="3.125" customWidth="1"/>
-    <col min="20" max="20" width="4" customWidth="1"/>
-    <col min="21" max="25" width="3.125" customWidth="1"/>
-    <col min="26" max="26" width="4" customWidth="1"/>
-    <col min="27" max="31" width="3.125" customWidth="1"/>
-    <col min="32" max="32" width="4" customWidth="1"/>
-    <col min="33" max="37" width="3.125" customWidth="1"/>
-    <col min="38" max="38" width="4" customWidth="1"/>
-    <col min="39" max="39" width="3.125" customWidth="1"/>
-    <col min="40" max="40" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="3.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="3.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4" style="1" customWidth="1"/>
+    <col min="9" max="13" width="3.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4" style="1" customWidth="1"/>
+    <col min="15" max="19" width="3.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="4" style="1" customWidth="1"/>
+    <col min="21" max="25" width="3.125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="4" style="1" customWidth="1"/>
+    <col min="27" max="31" width="3.125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="4" style="1" customWidth="1"/>
+    <col min="33" max="37" width="3.125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="4" style="1" customWidth="1"/>
+    <col min="39" max="39" width="3.125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="3.625" style="1" customWidth="1"/>
+    <col min="41" max="42" width="3.375" customWidth="1"/>
+    <col min="43" max="43" width="3.625" customWidth="1"/>
+    <col min="44" max="45" width="3.75" customWidth="1"/>
+    <col min="46" max="46" width="3.875" customWidth="1"/>
+    <col min="47" max="47" width="3.5" customWidth="1"/>
+    <col min="48" max="48" width="3.25" customWidth="1"/>
+    <col min="49" max="49" width="4.375" customWidth="1"/>
+    <col min="50" max="50" width="3.625" customWidth="1"/>
+    <col min="51" max="51" width="3.5" customWidth="1"/>
+    <col min="52" max="52" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:40">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:52">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="4"/>
     </row>
-    <row r="2" customFormat="1" spans="1:40">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:52">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="3" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
+      <c r="AZ2" s="5"/>
     </row>
-    <row r="3" customFormat="1" spans="1:40">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:52">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="3" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
     </row>
-    <row r="4" customFormat="1" ht="40" customHeight="1" spans="1:40">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="40" customHeight="1" spans="1:52">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="7"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="7"/>
+      <c r="AN4" s="7"/>
+      <c r="AO4" s="7"/>
+      <c r="AP4" s="7"/>
+      <c r="AQ4" s="7"/>
+      <c r="AR4" s="7"/>
+      <c r="AS4" s="7"/>
+      <c r="AT4" s="7"/>
+      <c r="AU4" s="7"/>
+      <c r="AV4" s="7"/>
+      <c r="AW4" s="7"/>
+      <c r="AX4" s="7"/>
+      <c r="AY4" s="7"/>
+      <c r="AZ4" s="8"/>
     </row>
-    <row r="5" customFormat="1" spans="1:40">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="24" spans="1:52">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="4" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="4" t="s">
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="4" t="s">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="4" t="s">
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="4" t="s">
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="4" t="s">
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="9" t="s">
         <v>15</v>
       </c>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="10"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="10"/>
+      <c r="AW5" s="10"/>
+      <c r="AX5" s="10"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="6" customFormat="1" ht="142" customHeight="1" spans="1:40">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="4" t="s">
+    <row r="6" ht="142" customHeight="1" spans="1:52">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="F6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="4" t="s">
+      <c r="H6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="K6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="L6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="M6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R6" s="4" t="s">
+      <c r="N6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="Q6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="T6" s="4" t="s">
+      <c r="R6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="S6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="X6" s="4" t="s">
+      <c r="T6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="W6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="Z6" s="4" t="s">
+      <c r="X6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AA6" s="4" t="s">
+      <c r="Y6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AB6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD6" s="4" t="s">
+      <c r="Z6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AE6" s="4" t="s">
+      <c r="AC6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AF6" s="4" t="s">
+      <c r="AD6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AG6" s="4" t="s">
+      <c r="AE6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AH6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ6" s="4" t="s">
+      <c r="AF6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AK6" s="4" t="s">
+      <c r="AI6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AL6" s="4" t="s">
+      <c r="AJ6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AM6" s="4" t="s">
+      <c r="AK6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AN6" s="2"/>
+      <c r="AL6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AS6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AV6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ6" s="13"/>
     </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:40">
-      <c r="A7" s="5">
+    <row r="7" ht="27" customHeight="1" spans="1:52">
+      <c r="A7" s="14">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="14">
         <v>20</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="14">
         <v>20</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="14">
         <v>20</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="14">
         <v>20</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="14">
         <v>100</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="14">
         <v>20</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="14">
         <v>40</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="14">
         <v>40</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="14">
         <v>40</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="14">
         <v>40</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="14">
         <v>100</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="14">
         <v>40</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="14">
         <v>20</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="14">
         <v>20</v>
       </c>
-      <c r="R7" s="5">
+      <c r="R7" s="14">
         <v>20</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="14">
         <v>20</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="14">
         <v>100</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="14">
         <v>20</v>
       </c>
-      <c r="V7" s="5">
+      <c r="V7" s="14">
         <v>10</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="14">
         <v>10</v>
       </c>
-      <c r="X7" s="5">
+      <c r="X7" s="14">
         <v>10</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="14">
         <v>10</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="14">
         <v>100</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AA7" s="14">
         <v>10</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AB7" s="14">
         <v>5</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AC7" s="14">
         <v>5</v>
       </c>
-      <c r="AD7" s="5">
+      <c r="AD7" s="14">
         <v>5</v>
       </c>
-      <c r="AE7" s="5">
+      <c r="AE7" s="14">
         <v>5</v>
       </c>
-      <c r="AF7" s="5">
+      <c r="AF7" s="14">
         <v>100</v>
       </c>
-      <c r="AG7" s="5">
+      <c r="AG7" s="14">
         <v>5</v>
       </c>
-      <c r="AH7" s="5">
+      <c r="AH7" s="14">
         <v>5</v>
       </c>
-      <c r="AI7" s="5">
+      <c r="AI7" s="14">
         <v>5</v>
       </c>
-      <c r="AJ7" s="5">
+      <c r="AJ7" s="14">
         <v>5</v>
       </c>
-      <c r="AK7" s="5">
+      <c r="AK7" s="14">
         <v>5</v>
       </c>
-      <c r="AL7" s="5">
+      <c r="AL7" s="14">
         <v>100</v>
       </c>
-      <c r="AM7" s="5">
+      <c r="AM7" s="14">
         <v>5</v>
       </c>
-      <c r="AN7" s="5">
+      <c r="AN7" s="14"/>
+      <c r="AO7" s="14"/>
+      <c r="AP7" s="14"/>
+      <c r="AQ7" s="14"/>
+      <c r="AR7" s="14"/>
+      <c r="AS7" s="14"/>
+      <c r="AT7" s="14"/>
+      <c r="AU7" s="14"/>
+      <c r="AV7" s="14"/>
+      <c r="AW7" s="14"/>
+      <c r="AX7" s="14"/>
+      <c r="AY7" s="14"/>
+      <c r="AZ7" s="14">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="14">
+    <mergeCell ref="A1:AZ1"/>
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="T2:AN2"/>
+    <mergeCell ref="T2:AZ2"/>
     <mergeCell ref="A3:S3"/>
-    <mergeCell ref="T3:AN3"/>
-    <mergeCell ref="A4:AN4"/>
+    <mergeCell ref="T3:AZ3"/>
+    <mergeCell ref="A4:AZ4"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="J5:O5"/>
     <mergeCell ref="P5:U5"/>
     <mergeCell ref="V5:AA5"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AN5:AS5"/>
+    <mergeCell ref="AT5:AY5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape"/>
